--- a/data/trans_orig/IQ09_D-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en días que llevan sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en días que llevan sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,79</t>
+          <t>0,53; 4,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 12,98</t>
+          <t>0,7; 12,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,93</t>
+          <t>0,0; 17,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,36</t>
+          <t>0,37; 3,15</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,24</t>
+          <t>0,0; 13,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,24</t>
+          <t>0,0; 13,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,91</t>
+          <t>0,64; 6,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1036,22 +1036,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
     </row>
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,24</t>
+          <t>0,86; 7,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,67</t>
+          <t>0,46; 6,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,42 +1156,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,14</t>
+          <t>0,0; 8,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,97</t>
+          <t>0,14; 3,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 9,52</t>
+          <t>0,62; 9,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,33</t>
+          <t>1,24; 6,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,28</t>
+          <t>0,54; 3,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,29</t>
+          <t>0,32; 5,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,9</t>
+          <t>0,18; 3,79</t>
         </is>
       </c>
     </row>
@@ -1281,27 +1281,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 6,4</t>
+          <t>0,11; 6,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 4,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 10,51</t>
+          <t>0,41; 10,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 8,06</t>
+          <t>0,0; 9,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,27 +1311,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 14,13</t>
+          <t>3,06; 15,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,37</t>
+          <t>0,86; 8,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,44</t>
+          <t>0,47; 5,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 6,12</t>
+          <t>0,06; 5,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 10,94</t>
+          <t>2,15; 11,61</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,26</t>
+          <t>0,75; 11,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,04</t>
+          <t>0,0; 9,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,48</t>
+          <t>0,0; 15,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,21</t>
+          <t>0,0; 8,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,06</t>
+          <t>0,0; 7,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,06; 11,76</t>
+          <t>0,07; 10,44</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,58</t>
+          <t>1,34; 6,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,89</t>
+          <t>1,3; 4,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,99</t>
+          <t>0,63; 4,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,34</t>
+          <t>0,6; 3,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,66</t>
+          <t>1,66; 5,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,55</t>
+          <t>0,26; 2,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,01</t>
+          <t>0,4; 3,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,22</t>
+          <t>1,14; 5,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,15</t>
+          <t>1,69; 5,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,92</t>
+          <t>0,98; 3,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,75</t>
+          <t>0,74; 2,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,0</t>
+          <t>1,22; 3,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_D-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,6</t>
+          <t>0,59; 4,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 15,94</t>
+          <t>0,95; 15,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 12,37</t>
+          <t>1,39; 13,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,75</t>
+          <t>0,0; 18,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,15</t>
+          <t>0,43; 3,14</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,49</t>
+          <t>0,64; 6,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,96</t>
+          <t>0,89; 8,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,2</t>
+          <t>0,38; 5,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,13</t>
+          <t>0,0; 8,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,13</t>
+          <t>0,0; 6,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,11</t>
+          <t>0,14; 2,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 9,46</t>
+          <t>0,61; 8,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,5</t>
+          <t>1,25; 6,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,22</t>
+          <t>0,54; 3,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,43</t>
+          <t>0,32; 5,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,79</t>
+          <t>0,17; 3,99</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 6,84</t>
+          <t>0,15; 7,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 10,28</t>
+          <t>0,4; 10,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,32</t>
+          <t>0,0; 7,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,27 +1311,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,06; 15,19</t>
+          <t>2,6; 15,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,67</t>
+          <t>0,95; 8,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,0</t>
+          <t>0,52; 5,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,78</t>
+          <t>0,06; 5,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 11,61</t>
+          <t>2,16; 11,26</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 11,26</t>
+          <t>0,0; 11,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,56</t>
+          <t>0,0; 10,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,11</t>
+          <t>0,0; 15,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,2</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>0,0; 8,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 10,44</t>
+          <t>0,06; 10,2</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,36</t>
+          <t>1,29; 6,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,9</t>
+          <t>1,23; 4,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,09</t>
+          <t>0,65; 4,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,41</t>
+          <t>0,53; 3,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,65</t>
+          <t>1,52; 5,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,65</t>
+          <t>0,26; 2,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,23</t>
+          <t>0,47; 3,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,49</t>
+          <t>1,08; 5,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,06</t>
+          <t>1,94; 5,19</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,12</t>
+          <t>0,93; 2,97</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,71</t>
+          <t>0,73; 2,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,86</t>
+          <t>1,19; 4,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_D-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D-Clase-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,62 +648,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,86</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7,92</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>17,75</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,86</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1,75</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5,74</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9,02</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5,74</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9,02</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,22</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,95; 15,94</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,85</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 15,0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>15,0; 20,0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,59; 4,75</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,95; 15,82</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0,46; 4,65</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0,7; 12,98</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 18,93</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1,39; 13,64</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 18,93</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,14</t>
+          <t>0,38; 3,26</t>
         </is>
       </c>
     </row>
@@ -788,49 +788,49 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,35</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,13</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,25</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,59</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2,17</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3,77</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3,77</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3,04</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>0,92</t>
         </is>
       </c>
     </row>
@@ -856,47 +856,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 12,24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,58</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,72</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>0,65; 10,0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1,4; 12,71</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0,0; 7,0</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,33</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,57</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,71</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>0,0; 12,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,39</t>
+          <t>0,68; 6,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
     </row>
@@ -928,49 +928,49 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,36</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,4</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2,0</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0,61</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0,28</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,65</t>
         </is>
       </c>
     </row>
@@ -996,52 +996,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>0,0; 1,0</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>0,0; 1,0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,41</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,87</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,02</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,53</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,84</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,21</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,13</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,12</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,02</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>4,12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,95</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,24</t>
+          <t>0,0; 8,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,68</t>
+          <t>0,15; 2,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,61; 9,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,21</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>0,86; 8,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,96</t>
+          <t>0,37; 5,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 8,4</t>
+          <t>0,0; 0,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 11,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,15</t>
+          <t>1,31; 6,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,18</t>
+          <t>0,51; 3,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,42</t>
+          <t>0,33; 5,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,99</t>
+          <t>0,48; 5,55</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,26</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7,1</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,57</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,11</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,26</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,14</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>5,02</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,4; 10,51</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0,31; 8,06</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2,42; 14,78</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 7,0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,21</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,15; 7,07</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,64</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,4; 10,5</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,77</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,15; 6,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 15,23</t>
+          <t>0,0; 4,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,66</t>
+          <t>0,87; 8,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,06</t>
+          <t>0,67; 5,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,21</t>
+          <t>0,11; 6,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 11,26</t>
+          <t>1,83; 11,42</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4,33</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3,07</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4,68</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,33</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>2,86</t>
         </is>
       </c>
     </row>
@@ -1416,47 +1416,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 11,26</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,04</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 17,37</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,8</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,26</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,2</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,69</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,0; 8,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,37</t>
+          <t>0,0; 9,06</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,06; 10,2</t>
+          <t>0,05; 11,95</t>
         </is>
       </c>
     </row>
@@ -1488,49 +1488,49 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2,68</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3,24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2,71</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,75</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2,06</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3,25</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2,65</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>1,77</t>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>2,42</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,54</t>
+          <t>1,6; 5,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,76</t>
+          <t>0,26; 2,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,09</t>
+          <t>0,45; 3,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,55</t>
+          <t>1,04; 5,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,45</t>
+          <t>1,32; 6,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,76</t>
+          <t>1,18; 4,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,22</t>
+          <t>0,66; 3,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,71</t>
+          <t>0,93; 4,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,19</t>
+          <t>1,87; 5,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,97</t>
+          <t>0,96; 2,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,71</t>
+          <t>0,76; 2,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,06</t>
+          <t>1,36; 4,32</t>
         </is>
       </c>
     </row>
